--- a/仕様.xlsx
+++ b/仕様.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\com\source\repos\Stealth\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\source\repos\Stealth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A67A63-9002-49C5-90DE-9DB9367FF078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8232FA19-5DBF-4F21-AA4C-63AAC3D75083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15420" yWindow="4290" windowWidth="28800" windowHeight="11295" activeTab="3" xr2:uid="{09C5898A-1FAC-4130-8D23-D77D5BC0504D}"/>
+    <workbookView xWindow="-21675" yWindow="2580" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{09C5898A-1FAC-4130-8D23-D77D5BC0504D}"/>
   </bookViews>
   <sheets>
     <sheet name="本編" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3406,33 +3403,33 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
@@ -3440,46 +3437,45 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3529,26 +3525,22 @@
       <c r="G5" s="3"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3594,12 +3586,12 @@
       <c r="G17" s="3"/>
     </row>
     <row r="19" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3613,70 +3605,38 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B943A84-14B2-4C2F-8C7D-0DBF879730FF}">
-  <dimension ref="B2:G11"/>
+  <dimension ref="B2:C9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C3" s="4" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C4" s="4" t="s">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="D6" s="4"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C9" s="4" t="s">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
